--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4094" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4071" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,10 +316,6 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -343,9 +339,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -388,12 +381,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -474,8 +461,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-1</t>
+    <t xml:space="preserve">bdl-1
+</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -512,6 +499,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -532,16 +522,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -578,9 +558,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -588,9 +565,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -609,8 +583,11 @@
     <t>Slice based on the request.url pattern</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>open</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -659,9 +636,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -671,8 +645,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -728,8 +702,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -783,9 +757,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -813,8 +784,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1474,15 +1445,15 @@
     <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.88671875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="62.87890625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="143.74609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="44.65625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
@@ -1929,16 +1900,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1949,10 +1920,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1975,16 +1946,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2034,7 +2005,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2043,16 +2014,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2063,10 +2034,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2089,16 +2060,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2124,32 +2095,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2157,16 +2128,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2177,10 +2148,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2203,16 +2174,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2262,7 +2233,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2271,30 +2242,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2317,16 +2288,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2337,78 +2308,78 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2431,16 +2402,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2490,7 +2461,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2499,30 +2470,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2545,16 +2516,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2604,7 +2575,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2613,16 +2584,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2633,10 +2604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2659,16 +2630,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2718,7 +2689,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2727,16 +2698,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2747,10 +2718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2773,13 +2744,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2830,7 +2801,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2848,7 +2819,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2859,14 +2830,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2885,16 +2856,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2932,19 +2903,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2953,16 +2924,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2973,14 +2944,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2999,19 +2970,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3060,7 +3031,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3069,10 +3040,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3089,10 +3060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3115,17 +3086,15 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3174,7 +3143,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3183,16 +3152,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3203,10 +3172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3229,17 +3198,15 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3288,7 +3255,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3297,16 +3264,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3317,10 +3284,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3343,13 +3310,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3388,19 +3355,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3409,16 +3376,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3429,10 +3396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3455,13 +3422,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3512,7 +3479,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3530,7 +3497,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3541,14 +3508,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3567,16 +3534,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3614,19 +3581,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3635,16 +3602,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3655,14 +3622,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3681,19 +3648,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3742,7 +3709,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3751,10 +3718,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3771,10 +3738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3800,10 +3767,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3854,7 +3821,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3866,7 +3833,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3883,10 +3850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3909,16 +3876,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3968,7 +3935,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3977,16 +3944,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3997,10 +3964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4023,13 +3990,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4080,7 +4047,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4098,7 +4065,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4109,10 +4076,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4135,13 +4102,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4192,7 +4159,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4201,16 +4168,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4221,10 +4188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4247,13 +4214,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4304,7 +4271,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4322,7 +4289,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4333,14 +4300,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4359,16 +4326,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4406,19 +4373,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4427,16 +4394,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4447,14 +4414,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4473,19 +4440,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4534,7 +4501,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4543,10 +4510,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4563,10 +4530,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4589,16 +4556,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4624,13 +4591,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4648,7 +4615,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4657,16 +4624,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4677,10 +4644,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4703,16 +4670,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4762,7 +4729,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4771,16 +4738,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4791,10 +4758,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4817,13 +4784,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4874,7 +4841,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4883,16 +4850,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4903,10 +4870,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4929,13 +4896,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4986,7 +4953,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5004,7 +4971,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5015,14 +4982,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5041,16 +5008,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5088,19 +5055,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5109,16 +5076,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5129,14 +5096,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5155,19 +5122,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5216,7 +5183,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5225,10 +5192,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5245,10 +5212,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5271,17 +5238,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5306,13 +5271,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5330,7 +5295,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5339,16 +5304,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5359,10 +5324,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5385,16 +5350,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5444,7 +5409,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5453,16 +5418,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5473,10 +5438,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5499,17 +5464,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5558,7 +5521,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5567,16 +5530,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5587,10 +5550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5613,17 +5576,15 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5672,7 +5633,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5681,16 +5642,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5701,10 +5662,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5727,17 +5688,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5786,7 +5745,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5795,16 +5754,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5815,10 +5774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5841,17 +5800,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5900,7 +5857,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5909,16 +5866,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5929,10 +5886,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5955,13 +5912,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6012,7 +5969,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6021,16 +5978,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6041,10 +5998,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6067,13 +6024,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6124,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6142,7 +6099,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6153,14 +6110,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6179,16 +6136,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6226,19 +6183,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6247,16 +6204,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6267,14 +6224,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6293,19 +6250,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6354,7 +6311,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6363,10 +6320,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6383,10 +6340,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6409,17 +6366,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6468,7 +6423,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6477,16 +6432,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6497,10 +6452,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6523,17 +6478,15 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6582,7 +6535,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6591,16 +6544,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6611,10 +6564,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6637,16 +6590,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6696,7 +6649,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6705,16 +6658,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6725,10 +6678,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6751,16 +6704,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6810,7 +6763,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6819,16 +6772,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6839,10 +6792,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6865,16 +6818,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6924,7 +6877,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6942,7 +6895,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6953,13 +6906,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6981,13 +6934,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7038,7 +6991,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7047,16 +7000,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7067,10 +7020,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7093,13 +7046,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7150,7 +7103,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7168,7 +7121,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7179,14 +7132,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7205,16 +7158,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7252,19 +7205,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7273,16 +7226,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7293,14 +7246,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7319,19 +7272,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7380,7 +7333,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7389,10 +7342,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7409,10 +7362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7438,10 +7391,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7492,7 +7445,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7504,7 +7457,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7521,10 +7474,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7547,16 +7500,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7606,7 +7559,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7615,16 +7568,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7635,14 +7588,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7661,16 +7614,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7720,7 +7673,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7735,10 +7688,10 @@
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7749,10 +7702,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7775,13 +7728,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7832,7 +7785,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7841,16 +7794,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7861,10 +7814,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7887,13 +7840,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7944,7 +7897,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7962,7 +7915,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7973,14 +7926,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7999,16 +7952,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8046,19 +7999,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8067,16 +8020,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8087,14 +8040,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8113,19 +8066,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8174,7 +8127,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8183,10 +8136,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8203,10 +8156,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8229,16 +8182,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8264,13 +8217,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8288,7 +8241,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8297,16 +8250,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8317,10 +8270,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8343,16 +8296,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8402,7 +8355,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8411,16 +8364,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8431,10 +8384,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8457,13 +8410,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8514,7 +8467,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8523,16 +8476,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8543,10 +8496,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8569,13 +8522,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8626,7 +8579,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8644,7 +8597,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8655,14 +8608,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8681,16 +8634,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8728,19 +8681,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8749,16 +8702,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8769,14 +8722,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8795,19 +8748,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8856,7 +8809,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8865,10 +8818,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8885,10 +8838,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8911,17 +8864,15 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8931,7 +8882,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -8946,13 +8897,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8970,7 +8921,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8979,16 +8930,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8999,10 +8950,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9025,16 +8976,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9045,7 +8996,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9084,7 +9035,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9093,16 +9044,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9113,10 +9064,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9139,17 +9090,15 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9198,7 +9147,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9207,16 +9156,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9227,10 +9176,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9253,17 +9202,15 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9312,7 +9259,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9321,16 +9268,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9341,10 +9288,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9367,17 +9314,15 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9426,7 +9371,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9435,16 +9380,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9455,10 +9400,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9481,17 +9426,15 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9540,7 +9483,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9549,16 +9492,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9569,10 +9512,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9595,13 +9538,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9652,7 +9595,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9661,16 +9604,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9681,10 +9624,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9707,13 +9650,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9764,7 +9707,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9782,7 +9725,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9793,14 +9736,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9819,16 +9762,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9866,19 +9809,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9887,16 +9830,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9907,14 +9850,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9933,19 +9876,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9994,7 +9937,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10003,10 +9946,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10023,10 +9966,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10049,17 +9992,15 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10108,7 +10049,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10117,16 +10058,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10137,10 +10078,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10163,17 +10104,15 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10222,7 +10161,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10231,16 +10170,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10251,10 +10190,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10277,16 +10216,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10336,7 +10275,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10345,16 +10284,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10365,10 +10304,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10391,16 +10330,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10450,7 +10389,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10459,16 +10398,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10479,10 +10418,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10505,16 +10444,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10564,7 +10503,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10582,7 +10521,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10593,13 +10532,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10621,13 +10560,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10678,7 +10617,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10687,16 +10626,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10707,10 +10646,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10733,13 +10672,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10790,7 +10729,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10808,7 +10747,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10819,14 +10758,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10845,16 +10784,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10892,19 +10831,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10913,16 +10852,16 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10933,14 +10872,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10959,19 +10898,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11020,7 +10959,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11029,10 +10968,10 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11049,10 +10988,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11078,10 +11017,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11132,7 +11071,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11144,7 +11083,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11161,10 +11100,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11187,16 +11126,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11246,7 +11185,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11255,16 +11194,16 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ86" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11275,10 +11214,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11301,16 +11240,16 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11360,7 +11299,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11378,7 +11317,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11389,10 +11328,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11415,13 +11354,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11472,7 +11411,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11481,16 +11420,16 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11501,10 +11440,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11527,13 +11466,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11584,7 +11523,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11602,7 +11541,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11613,14 +11552,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11639,16 +11578,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11686,19 +11625,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11707,16 +11646,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11727,14 +11666,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11753,19 +11692,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11814,7 +11753,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11823,10 +11762,10 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11843,10 +11782,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11869,16 +11808,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11904,13 +11843,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11928,7 +11867,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11937,16 +11876,16 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ92" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -11957,10 +11896,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11983,16 +11922,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12042,7 +11981,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12051,16 +11990,16 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ93" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12071,10 +12010,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12097,13 +12036,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12154,7 +12093,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12163,16 +12102,16 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12183,10 +12122,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12209,13 +12148,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12266,7 +12205,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12284,7 +12223,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12295,14 +12234,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12321,16 +12260,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12368,19 +12307,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12389,16 +12328,16 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12409,14 +12348,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12435,19 +12374,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12496,7 +12435,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12505,10 +12444,10 @@
         <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12525,10 +12464,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12551,17 +12490,15 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12571,7 +12508,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -12586,13 +12523,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12610,7 +12547,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12619,16 +12556,16 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ98" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
@@ -12639,10 +12576,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12665,16 +12602,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12685,7 +12622,7 @@
         <v>77</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>77</v>
@@ -12724,7 +12661,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12733,16 +12670,16 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ99" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -12753,10 +12690,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12779,17 +12716,15 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12838,7 +12773,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12847,16 +12782,16 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ100" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -12867,10 +12802,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12893,17 +12828,15 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12952,7 +12885,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12961,16 +12894,16 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ101" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -12981,10 +12914,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13007,17 +12940,15 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13066,7 +12997,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13075,16 +13006,16 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ102" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13095,10 +13026,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13121,17 +13052,15 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13180,7 +13109,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13189,16 +13118,16 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ103" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13209,10 +13138,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13235,13 +13164,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13292,7 +13221,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13301,16 +13230,16 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13321,10 +13250,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13347,13 +13276,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13404,7 +13333,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13422,7 +13351,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13433,14 +13362,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13459,16 +13388,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13506,19 +13435,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13527,16 +13456,16 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13547,14 +13476,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13573,19 +13502,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O107" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13634,7 +13563,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13643,10 +13572,10 @@
         <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13663,10 +13592,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13689,17 +13618,15 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13748,7 +13675,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13757,16 +13684,16 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ108" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -13777,10 +13704,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13803,17 +13730,15 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13862,7 +13787,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13871,16 +13796,16 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ109" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -13891,10 +13816,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13917,16 +13842,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13976,7 +13901,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13985,16 +13910,16 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ110" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -14005,10 +13930,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14031,16 +13956,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14090,7 +14015,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14099,16 +14024,16 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ111" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14119,10 +14044,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14145,16 +14070,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14204,7 +14129,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14222,7 +14147,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14233,10 +14158,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14259,19 +14184,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14320,7 +14245,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14329,16 +14254,16 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ113" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11014,7 +11014,7 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>186</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -880,7 +880,7 @@
 MeasurementResultsTests</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bmi|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bodyheight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-temperature|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-weight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bp|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-heartrate|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-glucose|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-head-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-pain-severity|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-steps-by-day|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-waist-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-oxygen-sat}
+    <t xml:space="preserve">Observation {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bmi|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bodyheight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-temperature|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-body-weight|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-bp|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-heartrate|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-head-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-pain-severity|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-steps-by-day|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-waist-circumference|https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-fr-observation-oxygen-sat}
 </t>
   </si>
   <si>
@@ -11014,7 +11014,7 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>186</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
